--- a/data/trans_dic/P44A$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Habitat-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,79; 55,51</t>
+          <t>7,19; 54,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>19,23; 54,69</t>
+          <t>20,11; 57,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,07; 46,39</t>
+          <t>6,14; 46,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,95; 62,62</t>
+          <t>19,7; 60,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,94</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,1; 40,12</t>
+          <t>9,97; 43,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,44; 51,57</t>
+          <t>25,13; 52,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 1,75</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,25</t>
+          <t>0,0; 25,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,14; 20,68</t>
+          <t>2,05; 18,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,04</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,87; 54,99</t>
+          <t>21,52; 57,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 35,22</t>
+          <t>6,19; 35,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,39; 37,4</t>
+          <t>15,08; 37,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,73; 21,44</t>
+          <t>5,58; 21,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,21</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,34; 43,01</t>
+          <t>4,44; 46,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,89; 43,59</t>
+          <t>10,4; 42,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,72</t>
+          <t>0,0; 4,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,37; 53,91</t>
+          <t>16,08; 53,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 39,06</t>
+          <t>5,0; 38,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,2</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,67; 42,97</t>
+          <t>14,69; 42,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,02; 34,47</t>
+          <t>10,26; 34,69</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,93</t>
+          <t>0,33; 4,08</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 31,2</t>
+          <t>5,06; 27,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,52; 39,69</t>
+          <t>16,39; 41,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,72</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23,76; 61,77</t>
+          <t>20,41; 59,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,82; 49,99</t>
+          <t>14,46; 48,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,21; 37,97</t>
+          <t>16,03; 38,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,23; 38,24</t>
+          <t>18,84; 38,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,33</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,37; 24,91</t>
+          <t>9,85; 25,34</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,66; 30,06</t>
+          <t>16,52; 30,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,05</t>
+          <t>0,07; 1,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25,06; 44,39</t>
+          <t>26,28; 46,76</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>17,96; 34,86</t>
+          <t>18,11; 35,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,24</t>
+          <t>0,12; 1,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,96; 31,91</t>
+          <t>19,3; 32,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,62; 30,37</t>
+          <t>19,07; 29,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,89</t>
+          <t>0,17; 0,85</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon</t>
+          <t>Población a la que le han realizado otra prueba para detectar cáncer de cólon (tasa de respuesta: 98,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1944; 8438</t>
+          <t>1092; 8338</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5940; 16893</t>
+          <t>6212; 17892</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3225</t>
+          <t>0; 3043</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>923; 7052</t>
+          <t>933; 7077</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5355; 16007</t>
+          <t>5036; 15518</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1894</t>
+          <t>0; 2075</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3070; 12196</t>
+          <t>3032; 13205</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13797; 29114</t>
+          <t>14189; 29426</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3178</t>
+          <t>0; 3307</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6925</t>
+          <t>0; 6791</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>847; 8170</t>
+          <t>811; 7237</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7893</t>
+          <t>0; 7598</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7590; 20000</t>
+          <t>7825; 20861</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2114; 11859</t>
+          <t>2085; 12120</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2084</t>
+          <t>0; 2266</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9655; 23469</t>
+          <t>9462; 23250</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4194; 15691</t>
+          <t>4085; 15754</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6145</t>
+          <t>0; 6229</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1144; 11336</t>
+          <t>1170; 12374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3045; 13420</t>
+          <t>3201; 13162</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5038</t>
+          <t>0; 5048</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4326; 14244</t>
+          <t>4248; 14199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1008; 7930</t>
+          <t>1015; 7842</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4480</t>
+          <t>0; 4491</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7744; 22677</t>
+          <t>7754; 22495</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5630; 17612</t>
+          <t>5244; 17726</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>595; 7037</t>
+          <t>592; 7296</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2834; 12926</t>
+          <t>2097; 11596</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9666; 23222</t>
+          <t>9591; 24213</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 1385</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6881; 17890</t>
+          <t>5910; 17285</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5423; 18291</t>
+          <t>5289; 17783</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 1080</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10705; 26729</t>
+          <t>11283; 26756</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17334; 36366</t>
+          <t>17918; 36937</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1220</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10251; 27241</t>
+          <t>10773; 27710</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26601; 47997</t>
+          <t>26384; 47921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>509; 8172</t>
+          <t>516; 8265</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26798; 47477</t>
+          <t>28103; 50006</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20859; 40485</t>
+          <t>21031; 40709</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>747; 5927</t>
+          <t>594; 5537</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41016; 69024</t>
+          <t>41755; 70122</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>54103; 83751</t>
+          <t>52593; 82205</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2053; 11182</t>
+          <t>2137; 10686</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P44A$otras-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P44A$otras-Habitat-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,19; 54,85</t>
+          <t>7,75; 54,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>20,11; 57,92</t>
+          <t>17,66; 55,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 2,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,14; 46,56</t>
+          <t>6,16; 47,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>19,7; 60,71</t>
+          <t>20,97; 62,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>0,0; 2,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,97; 43,44</t>
+          <t>10,08; 41,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>25,13; 52,13</t>
+          <t>23,66; 51,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,75%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,74</t>
+          <t>0,0; 27,28</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,05; 18,32</t>
+          <t>2,05; 19,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,33; 3,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21,52; 57,36</t>
+          <t>20,89; 56,35</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,19; 35,99</t>
+          <t>6,27; 34,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,08; 37,05</t>
+          <t>14,02; 36,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,58; 21,53</t>
+          <t>5,39; 21,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,21; 1,93</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 46,95</t>
+          <t>7,93; 47,66</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>10,4; 42,75</t>
+          <t>10,24; 43,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,73</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,08; 53,74</t>
+          <t>15,56; 52,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 38,63</t>
+          <t>5,04; 39,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>0,0; 5,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,69; 42,63</t>
+          <t>15,67; 41,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,26; 34,69</t>
+          <t>10,78; 35,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 4,08</t>
+          <t>0,32; 3,55</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 27,99</t>
+          <t>6,88; 30,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,39; 41,39</t>
+          <t>15,53; 39,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,12 +1023,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20,41; 59,68</t>
+          <t>22,43; 60,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,46; 48,6</t>
+          <t>15,68; 47,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,03; 38,01</t>
+          <t>15,42; 37,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,84; 38,84</t>
+          <t>19,51; 37,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>9,85; 25,34</t>
+          <t>9,48; 25,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16,52; 30,01</t>
+          <t>16,79; 30,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,06</t>
+          <t>0,2; 1,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,28; 46,76</t>
+          <t>25,5; 44,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,11; 35,06</t>
+          <t>18,16; 35,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 1,16</t>
+          <t>0,12; 1,08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,3; 32,42</t>
+          <t>19,54; 32,02</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>19,07; 29,8</t>
+          <t>19,02; 29,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,85</t>
+          <t>0,27; 1,11</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>578</t>
+          <t>573</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>375</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>947</t>
+          <t>948</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1092; 8338</t>
+          <t>1178; 8270</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6212; 17892</t>
+          <t>5454; 17255</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3043</t>
+          <t>0; 3003</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>933; 7077</t>
+          <t>936; 7189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>5036; 15518</t>
+          <t>5360; 15898</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 2075</t>
+          <t>0; 2124</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3032; 13205</t>
+          <t>3065; 12568</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14189; 29426</t>
+          <t>13358; 28807</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3307</t>
+          <t>0; 3603</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1778</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>432</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2211</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 6791</t>
+          <t>0; 7196</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>811; 7237</t>
+          <t>811; 7716</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 7598</t>
+          <t>503; 4863</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7825; 20861</t>
+          <t>7599; 20493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2085; 12120</t>
+          <t>2112; 11501</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2266</t>
+          <t>0; 2194</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9462; 23250</t>
+          <t>8797; 22755</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4085; 15754</t>
+          <t>3945; 15973</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6229</t>
+          <t>604; 5690</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2370</t>
+          <t>2507</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1170; 12374</t>
+          <t>2089; 12562</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3201; 13162</t>
+          <t>3154; 13302</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5048</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4248; 14199</t>
+          <t>4111; 13962</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1015; 7842</t>
+          <t>1024; 8011</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4491</t>
+          <t>0; 4290</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7754; 22495</t>
+          <t>8269; 21964</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5244; 17726</t>
+          <t>5510; 17895</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>592; 7296</t>
+          <t>655; 7218</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2097; 11596</t>
+          <t>2849; 12486</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9591; 24213</t>
+          <t>9085; 23281</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5910; 17285</t>
+          <t>6496; 17521</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5289; 17783</t>
+          <t>5736; 17413</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>11283; 26756</t>
+          <t>10855; 26461</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17918; 36937</t>
+          <t>18554; 36032</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3475</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2131</t>
+          <t>2190</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5499</t>
+          <t>5665</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10773; 27710</t>
+          <t>10363; 27833</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26384; 47921</t>
+          <t>26818; 48850</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>516; 8265</t>
+          <t>1134; 8062</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28103; 50006</t>
+          <t>27274; 47331</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>21031; 40709</t>
+          <t>21083; 41399</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>594; 5537</t>
+          <t>656; 5722</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41755; 70122</t>
+          <t>42263; 69254</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>52593; 82205</t>
+          <t>52459; 81742</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2137; 10686</t>
+          <t>2978; 12210</t>
         </is>
       </c>
     </row>
